--- a/Online Assessment 0/web_resources/Data files for Assessments/Online Assessment 0/Data3_41.xlsx
+++ b/Online Assessment 0/web_resources/Data files for Assessments/Online Assessment 0/Data3_41.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C51"/>
+  <dimension ref="A1:C201"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -362,12 +362,12 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Response</t>
+          <t>TrialOutcome</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Perfectionism</t>
+          <t>IV</t>
         </is>
       </c>
     </row>
@@ -378,10 +378,10 @@
         </is>
       </c>
       <c r="B2">
-        <v>0.301898736964768</v>
+        <v>0.3699500305406957</v>
       </c>
       <c r="C2">
-        <v>0.5771137010295504</v>
+        <v>-0.6793027309293614</v>
       </c>
     </row>
     <row r="3">
@@ -391,10 +391,10 @@
         </is>
       </c>
       <c r="B3">
-        <v>-0.3703345944378744</v>
+        <v>-1.673337768718941</v>
       </c>
       <c r="C3">
-        <v>-0.006659838265417051</v>
+        <v>-0.956315439050111</v>
       </c>
     </row>
     <row r="4">
@@ -404,10 +404,10 @@
         </is>
       </c>
       <c r="B4">
-        <v>0.2612930126390348</v>
+        <v>0.7596714309003021</v>
       </c>
       <c r="C4">
-        <v>0.817301272367343</v>
+        <v>-0.9751470152371658</v>
       </c>
     </row>
     <row r="5">
@@ -417,10 +417,10 @@
         </is>
       </c>
       <c r="B5">
-        <v>0.7227362965066546</v>
+        <v>1.07570105806</v>
       </c>
       <c r="C5">
-        <v>-0.2664529893564381</v>
+        <v>-0.06715782201271447</v>
       </c>
     </row>
     <row r="6">
@@ -430,10 +430,10 @@
         </is>
       </c>
       <c r="B6">
-        <v>0.3557763115776471</v>
+        <v>-0.5864827102442245</v>
       </c>
       <c r="C6">
-        <v>0.8969811733552165</v>
+        <v>0.5548947393060535</v>
       </c>
     </row>
     <row r="7">
@@ -443,10 +443,10 @@
         </is>
       </c>
       <c r="B7">
-        <v>0.24543279586427</v>
+        <v>-0.2636510995890993</v>
       </c>
       <c r="C7">
-        <v>-1.110788446190568</v>
+        <v>-0.9801223351576325</v>
       </c>
     </row>
     <row r="8">
@@ -456,10 +456,10 @@
         </is>
       </c>
       <c r="B8">
-        <v>-1.390390743913039</v>
+        <v>-0.1354978265836558</v>
       </c>
       <c r="C8">
-        <v>0.05130941879397655</v>
+        <v>-0.4811995292642897</v>
       </c>
     </row>
     <row r="9">
@@ -469,10 +469,10 @@
         </is>
       </c>
       <c r="B9">
-        <v>0.8785013253890406</v>
+        <v>1.273460832645674</v>
       </c>
       <c r="C9">
-        <v>-0.7765960314884192</v>
+        <v>-1.143206819920098</v>
       </c>
     </row>
     <row r="10">
@@ -482,10 +482,10 @@
         </is>
       </c>
       <c r="B10">
-        <v>0.2706256782249515</v>
+        <v>-0.3979766526334123</v>
       </c>
       <c r="C10">
-        <v>-0.6206072467639785</v>
+        <v>1.140733246789379</v>
       </c>
     </row>
     <row r="11">
@@ -495,10 +495,10 @@
         </is>
       </c>
       <c r="B11">
-        <v>-0.2101020273315393</v>
+        <v>-0.5788947511994371</v>
       </c>
       <c r="C11">
-        <v>-0.3240823278706328</v>
+        <v>-1.722717927915353</v>
       </c>
     </row>
     <row r="12">
@@ -508,10 +508,10 @@
         </is>
       </c>
       <c r="B12">
-        <v>-0.8216505666283093</v>
+        <v>0.2601091008374278</v>
       </c>
       <c r="C12">
-        <v>1.573395285032424</v>
+        <v>0.5860499740315669</v>
       </c>
     </row>
     <row r="13">
@@ -521,10 +521,10 @@
         </is>
       </c>
       <c r="B13">
-        <v>-0.3495011858903863</v>
+        <v>1.359805411466926</v>
       </c>
       <c r="C13">
-        <v>-0.07389161100435743</v>
+        <v>-1.501381116522876</v>
       </c>
     </row>
     <row r="14">
@@ -534,10 +534,10 @@
         </is>
       </c>
       <c r="B14">
-        <v>0.592399428670131</v>
+        <v>0.2060874331239327</v>
       </c>
       <c r="C14">
-        <v>-0.3697552105874216</v>
+        <v>-0.03310568881886399</v>
       </c>
     </row>
     <row r="15">
@@ -547,10 +547,10 @@
         </is>
       </c>
       <c r="B15">
-        <v>0.5330757162767573</v>
+        <v>-0.8963324086386694</v>
       </c>
       <c r="C15">
-        <v>-0.09237057552396291</v>
+        <v>-0.9916111691502631</v>
       </c>
     </row>
     <row r="16">
@@ -560,10 +560,10 @@
         </is>
       </c>
       <c r="B16">
-        <v>-0.7571978559527109</v>
+        <v>1.244510794534572</v>
       </c>
       <c r="C16">
-        <v>0.6035825930745523</v>
+        <v>0.8382411116609909</v>
       </c>
     </row>
     <row r="17">
@@ -573,10 +573,10 @@
         </is>
       </c>
       <c r="B17">
-        <v>0.8131970752538455</v>
+        <v>0.8258166375650531</v>
       </c>
       <c r="C17">
-        <v>0.2636351155687208</v>
+        <v>0.00369082808587945</v>
       </c>
     </row>
     <row r="18">
@@ -586,10 +586,10 @@
         </is>
       </c>
       <c r="B18">
-        <v>1.028815003820374</v>
+        <v>-0.04399212547565784</v>
       </c>
       <c r="C18">
-        <v>1.003299357907215</v>
+        <v>-1.363900878984117</v>
       </c>
     </row>
     <row r="19">
@@ -599,10 +599,10 @@
         </is>
       </c>
       <c r="B19">
-        <v>-1.998359151281454</v>
+        <v>-1.065476481039367</v>
       </c>
       <c r="C19">
-        <v>0.6920791840552555</v>
+        <v>0.828797971463657</v>
       </c>
     </row>
     <row r="20">
@@ -612,10 +612,10 @@
         </is>
       </c>
       <c r="B20">
-        <v>1.397019524624325</v>
+        <v>0.3958153165240951</v>
       </c>
       <c r="C20">
-        <v>0.5788085788387782</v>
+        <v>1.211902050238462</v>
       </c>
     </row>
     <row r="21">
@@ -625,10 +625,10 @@
         </is>
       </c>
       <c r="B21">
-        <v>-0.613956264649085</v>
+        <v>0.005348759926925808</v>
       </c>
       <c r="C21">
-        <v>0.05151507243483577</v>
+        <v>-0.3178409592325294</v>
       </c>
     </row>
     <row r="22">
@@ -638,10 +638,10 @@
         </is>
       </c>
       <c r="B22">
-        <v>-1.807512417037457</v>
+        <v>0.5648329944074487</v>
       </c>
       <c r="C22">
-        <v>1.005480129432546</v>
+        <v>0.1355480721916095</v>
       </c>
     </row>
     <row r="23">
@@ -651,10 +651,10 @@
         </is>
       </c>
       <c r="B23">
-        <v>0.6065765099996746</v>
+        <v>0.002145754100830836</v>
       </c>
       <c r="C23">
-        <v>-0.6318476766807793</v>
+        <v>1.432941262289974</v>
       </c>
     </row>
     <row r="24">
@@ -664,10 +664,10 @@
         </is>
       </c>
       <c r="B24">
-        <v>-1.034055065589275</v>
+        <v>0.4534875027812031</v>
       </c>
       <c r="C24">
-        <v>-0.4995559617809484</v>
+        <v>0.3290515356601444</v>
       </c>
     </row>
     <row r="25">
@@ -677,10 +677,10 @@
         </is>
       </c>
       <c r="B25">
-        <v>-0.1993463778973571</v>
+        <v>1.029165112593154</v>
       </c>
       <c r="C25">
-        <v>1.654784833095824</v>
+        <v>-1.371226420712276</v>
       </c>
     </row>
     <row r="26">
@@ -690,10 +690,10 @@
         </is>
       </c>
       <c r="B26">
-        <v>0.7156197196142062</v>
+        <v>-0.2840854851144889</v>
       </c>
       <c r="C26">
-        <v>-0.7529423647128335</v>
+        <v>-0.3129310577498969</v>
       </c>
     </row>
     <row r="27">
@@ -703,10 +703,10 @@
         </is>
       </c>
       <c r="B27">
-        <v>-1.362860231739576</v>
+        <v>-1.647039499099108</v>
       </c>
       <c r="C27">
-        <v>1.840935776156602</v>
+        <v>0.7995150807150821</v>
       </c>
     </row>
     <row r="28">
@@ -716,10 +716,10 @@
         </is>
       </c>
       <c r="B28">
-        <v>0.2535698695644168</v>
+        <v>0.3572279407607545</v>
       </c>
       <c r="C28">
-        <v>-0.3374411126077952</v>
+        <v>1.189733671403911</v>
       </c>
     </row>
     <row r="29">
@@ -729,10 +729,10 @@
         </is>
       </c>
       <c r="B29">
-        <v>-0.3743014883800647</v>
+        <v>-0.8771260870916398</v>
       </c>
       <c r="C29">
-        <v>0.1445009038135579</v>
+        <v>1.772450995757786</v>
       </c>
     </row>
     <row r="30">
@@ -742,10 +742,10 @@
         </is>
       </c>
       <c r="B30">
-        <v>3.006957785045819</v>
+        <v>0.5046821283150513</v>
       </c>
       <c r="C30">
-        <v>-0.1454809300420508</v>
+        <v>0.06640296804545773</v>
       </c>
     </row>
     <row r="31">
@@ -755,10 +755,10 @@
         </is>
       </c>
       <c r="B31">
-        <v>2.244999500459938</v>
+        <v>0.8553010835897615</v>
       </c>
       <c r="C31">
-        <v>-0.76747534905065</v>
+        <v>1.405608624812169</v>
       </c>
     </row>
     <row r="32">
@@ -768,10 +768,10 @@
         </is>
       </c>
       <c r="B32">
-        <v>-0.3101561101250012</v>
+        <v>-0.06652056422117621</v>
       </c>
       <c r="C32">
-        <v>0.7158837469925083</v>
+        <v>-0.2178803356472182</v>
       </c>
     </row>
     <row r="33">
@@ -781,10 +781,10 @@
         </is>
       </c>
       <c r="B33">
-        <v>-1.350928703760392</v>
+        <v>2.442066601200594</v>
       </c>
       <c r="C33">
-        <v>-0.01827109983727593</v>
+        <v>-1.131451232681338</v>
       </c>
     </row>
     <row r="34">
@@ -794,10 +794,10 @@
         </is>
       </c>
       <c r="B34">
-        <v>-0.645575100247316</v>
+        <v>0.4768235172537264</v>
       </c>
       <c r="C34">
-        <v>0.475435512437164</v>
+        <v>1.319285438910593</v>
       </c>
     </row>
     <row r="35">
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="B35">
-        <v>-1.275286372656831</v>
+        <v>-0.610293499642826</v>
       </c>
       <c r="C35">
-        <v>0.03987250872712683</v>
+        <v>1.187482504961221</v>
       </c>
     </row>
     <row r="36">
@@ -820,10 +820,10 @@
         </is>
       </c>
       <c r="B36">
-        <v>-1.719889703075596</v>
+        <v>1.476487823952693</v>
       </c>
       <c r="C36">
-        <v>2.372359299123713</v>
+        <v>0.0735279264207237</v>
       </c>
     </row>
     <row r="37">
@@ -833,10 +833,10 @@
         </is>
       </c>
       <c r="B37">
-        <v>-0.2297798348109947</v>
+        <v>-1.632282424298462</v>
       </c>
       <c r="C37">
-        <v>0.2815736804623192</v>
+        <v>0.1492657416876172</v>
       </c>
     </row>
     <row r="38">
@@ -846,10 +846,10 @@
         </is>
       </c>
       <c r="B38">
-        <v>1.575393030676044</v>
+        <v>-0.7274935447448433</v>
       </c>
       <c r="C38">
-        <v>0.3531087186311849</v>
+        <v>0.647210894090549</v>
       </c>
     </row>
     <row r="39">
@@ -859,10 +859,10 @@
         </is>
       </c>
       <c r="B39">
-        <v>-0.05639977973436594</v>
+        <v>0.6575902250735775</v>
       </c>
       <c r="C39">
-        <v>-0.3725649979786718</v>
+        <v>-1.095298536298873</v>
       </c>
     </row>
     <row r="40">
@@ -872,10 +872,10 @@
         </is>
       </c>
       <c r="B40">
-        <v>-1.142216734066807</v>
+        <v>0.9711595049915913</v>
       </c>
       <c r="C40">
-        <v>0.4902572732336801</v>
+        <v>0.7196427963661659</v>
       </c>
     </row>
     <row r="41">
@@ -885,10 +885,10 @@
         </is>
       </c>
       <c r="B41">
-        <v>-0.5703598701524811</v>
+        <v>-0.6529487973934983</v>
       </c>
       <c r="C41">
-        <v>-0.5550112475207357</v>
+        <v>0.5260050163940686</v>
       </c>
     </row>
     <row r="42">
@@ -898,10 +898,10 @@
         </is>
       </c>
       <c r="B42">
-        <v>0.2549211513460738</v>
+        <v>-0.276441044915458</v>
       </c>
       <c r="C42">
-        <v>0.06942113638056092</v>
+        <v>-0.2822008321814153</v>
       </c>
     </row>
     <row r="43">
@@ -911,10 +911,10 @@
         </is>
       </c>
       <c r="B43">
-        <v>-0.8265909838714529</v>
+        <v>-1.700038744195241</v>
       </c>
       <c r="C43">
-        <v>0.4890281561618793</v>
+        <v>1.690885483834614</v>
       </c>
     </row>
     <row r="44">
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="B44">
-        <v>0.6554059044134835</v>
+        <v>1.378153490198677</v>
       </c>
       <c r="C44">
-        <v>-0.5727103438721133</v>
+        <v>-2.189110368567652</v>
       </c>
     </row>
     <row r="45">
@@ -937,10 +937,10 @@
         </is>
       </c>
       <c r="B45">
-        <v>-3.026076476141309</v>
+        <v>-0.01939336991827349</v>
       </c>
       <c r="C45">
-        <v>1.61514242683351</v>
+        <v>0.9760317764011709</v>
       </c>
     </row>
     <row r="46">
@@ -950,10 +950,10 @@
         </is>
       </c>
       <c r="B46">
-        <v>1.571961093399329</v>
+        <v>0.1063260178945181</v>
       </c>
       <c r="C46">
-        <v>-0.04308262491215364</v>
+        <v>0.8182602639742941</v>
       </c>
     </row>
     <row r="47">
@@ -963,10 +963,10 @@
         </is>
       </c>
       <c r="B47">
-        <v>1.256914158504924</v>
+        <v>-0.929763895894591</v>
       </c>
       <c r="C47">
-        <v>-2.129454439477777</v>
+        <v>-0.6420103842122407</v>
       </c>
     </row>
     <row r="48">
@@ -976,10 +976,10 @@
         </is>
       </c>
       <c r="B48">
-        <v>-2.669827102941496</v>
+        <v>0.4551191714218764</v>
       </c>
       <c r="C48">
-        <v>1.904537089854114</v>
+        <v>-0.3607941328679533</v>
       </c>
     </row>
     <row r="49">
@@ -989,10 +989,10 @@
         </is>
       </c>
       <c r="B49">
-        <v>0.4105978100302807</v>
+        <v>2.236217986424002</v>
       </c>
       <c r="C49">
-        <v>0.506670046689061</v>
+        <v>-2.043199269769401</v>
       </c>
     </row>
     <row r="50">
@@ -1002,10 +1002,10 @@
         </is>
       </c>
       <c r="B50">
-        <v>0.5261913048963786</v>
+        <v>0.2470422554086052</v>
       </c>
       <c r="C50">
-        <v>-1.495090930726325</v>
+        <v>-0.08086640256250399</v>
       </c>
     </row>
     <row r="51">
@@ -1015,10 +1015,1960 @@
         </is>
       </c>
       <c r="B51">
-        <v>0.4014970511639431</v>
+        <v>0.02263089858084651</v>
       </c>
       <c r="C51">
-        <v>-0.03747441671409332</v>
+        <v>-0.3421634992249796</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="B52">
+        <v>-0.1427986169933894</v>
+      </c>
+      <c r="C52">
+        <v>-1.03010176595922</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="B53">
+        <v>-0.4640498716511294</v>
+      </c>
+      <c r="C53">
+        <v>1.267363041726544</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="B54">
+        <v>-0.2071744527532235</v>
+      </c>
+      <c r="C54">
+        <v>-1.323808725120315</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="B55">
+        <v>-0.1471466722699729</v>
+      </c>
+      <c r="C55">
+        <v>-1.055787148495444</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="B56">
+        <v>0.7836133233788296</v>
+      </c>
+      <c r="C56">
+        <v>0.4329499207273554</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="B57">
+        <v>-1.935959174434868</v>
+      </c>
+      <c r="C57">
+        <v>0.2205883515095545</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="B58">
+        <v>0.06948065810378745</v>
+      </c>
+      <c r="C58">
+        <v>0.2527934862205378</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="B59">
+        <v>2.443100968055462</v>
+      </c>
+      <c r="C59">
+        <v>-1.108674333651656</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="B60">
+        <v>-1.670026061981529</v>
+      </c>
+      <c r="C60">
+        <v>1.498101804425147</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="B61">
+        <v>1.300556050954399</v>
+      </c>
+      <c r="C61">
+        <v>1.717249937841787</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="B62">
+        <v>0.7560300660932757</v>
+      </c>
+      <c r="C62">
+        <v>-0.2311237391275345</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="B63">
+        <v>1.608559170559692</v>
+      </c>
+      <c r="C63">
+        <v>0.1021406021667833</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="B64">
+        <v>1.003287504655302</v>
+      </c>
+      <c r="C64">
+        <v>-1.386833995924415</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="B65">
+        <v>-0.4805551198718428</v>
+      </c>
+      <c r="C65">
+        <v>-1.216058021091484</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="B66">
+        <v>-0.2642705405268064</v>
+      </c>
+      <c r="C66">
+        <v>1.209390735122998</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="B67">
+        <v>-1.481404779537812</v>
+      </c>
+      <c r="C67">
+        <v>-0.1432027967528657</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="B68">
+        <v>-0.1488944356535402</v>
+      </c>
+      <c r="C68">
+        <v>-0.4944536790787847</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="B69">
+        <v>0.577143183584468</v>
+      </c>
+      <c r="C69">
+        <v>-0.714960944093446</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="B70">
+        <v>-1.860760151375284</v>
+      </c>
+      <c r="C70">
+        <v>-0.426979296374473</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="B71">
+        <v>-0.8000842632573461</v>
+      </c>
+      <c r="C71">
+        <v>-1.963909199299659</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="B72">
+        <v>0.4973860876963612</v>
+      </c>
+      <c r="C72">
+        <v>0.2502950153299169</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="B73">
+        <v>0.9541719033036752</v>
+      </c>
+      <c r="C73">
+        <v>-1.615677763926363</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="B74">
+        <v>0.5472638031498217</v>
+      </c>
+      <c r="C74">
+        <v>1.01106277331625</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="B75">
+        <v>-0.9112201006974051</v>
+      </c>
+      <c r="C75">
+        <v>-0.7984067278366318</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="B76">
+        <v>-1.454337872568033</v>
+      </c>
+      <c r="C76">
+        <v>-0.1059890155910109</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="B77">
+        <v>2.222861314380552</v>
+      </c>
+      <c r="C77">
+        <v>-1.080800809015457</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="B78">
+        <v>1.249729755229224</v>
+      </c>
+      <c r="C78">
+        <v>-0.3401255311826002</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="B79">
+        <v>-0.3727998013682375</v>
+      </c>
+      <c r="C79">
+        <v>0.1183875925676694</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="B80">
+        <v>0.9453888762841891</v>
+      </c>
+      <c r="C80">
+        <v>-0.05526292984542081</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="B81">
+        <v>-1.578131804698345</v>
+      </c>
+      <c r="C81">
+        <v>0.8917206732822973</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="B82">
+        <v>-0.7076126514118</v>
+      </c>
+      <c r="C82">
+        <v>0.8718814651109666</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="B83">
+        <v>0.3717637533707513</v>
+      </c>
+      <c r="C83">
+        <v>0.6476029223165438</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="B84">
+        <v>-0.6265200243060713</v>
+      </c>
+      <c r="C84">
+        <v>0.5773600062493496</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="B85">
+        <v>0.8313800768863129</v>
+      </c>
+      <c r="C85">
+        <v>-1.312089536613285</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="B86">
+        <v>-0.772437340516371</v>
+      </c>
+      <c r="C86">
+        <v>1.379713513246077</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="B87">
+        <v>0.6881430015727675</v>
+      </c>
+      <c r="C87">
+        <v>-0.1818641470906261</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="B88">
+        <v>-0.3201461096794174</v>
+      </c>
+      <c r="C88">
+        <v>0.1500176329696387</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="B89">
+        <v>-0.2330462009036466</v>
+      </c>
+      <c r="C89">
+        <v>-1.021950195437938</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="B90">
+        <v>0.6702748561909757</v>
+      </c>
+      <c r="C90">
+        <v>1.327111044149853</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="B91">
+        <v>-0.7278850178073378</v>
+      </c>
+      <c r="C91">
+        <v>1.217886048938265</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="B92">
+        <v>-0.02942403285561993</v>
+      </c>
+      <c r="C92">
+        <v>-1.15064745735555</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>92</t>
+        </is>
+      </c>
+      <c r="B93">
+        <v>-1.776937814324068</v>
+      </c>
+      <c r="C93">
+        <v>1.681440393192126</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="B94">
+        <v>-1.478067883938463</v>
+      </c>
+      <c r="C94">
+        <v>0.5378606779769032</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="B95">
+        <v>-0.8509949920671458</v>
+      </c>
+      <c r="C95">
+        <v>0.8621483888655304</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="B96">
+        <v>-0.7294616287795364</v>
+      </c>
+      <c r="C96">
+        <v>0.7738693061470205</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="B97">
+        <v>2.336847729318821</v>
+      </c>
+      <c r="C97">
+        <v>-1.028880760731044</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="B98">
+        <v>-0.7993960636105637</v>
+      </c>
+      <c r="C98">
+        <v>0.163568266476471</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="B99">
+        <v>0.4402601825670672</v>
+      </c>
+      <c r="C99">
+        <v>-0.7241883283889197</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="B100">
+        <v>-1.186210847345603</v>
+      </c>
+      <c r="C100">
+        <v>0.1872609260523346</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="B101">
+        <v>0.7434228213133717</v>
+      </c>
+      <c r="C101">
+        <v>-1.342812421966912</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="B102">
+        <v>0.5251489149299071</v>
+      </c>
+      <c r="C102">
+        <v>-2.388654061652154</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="B103">
+        <v>-1.794271719238711</v>
+      </c>
+      <c r="C103">
+        <v>1.341412231213633</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>103</t>
+        </is>
+      </c>
+      <c r="B104">
+        <v>-0.5377510084343007</v>
+      </c>
+      <c r="C104">
+        <v>-0.6391927064643241</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>104</t>
+        </is>
+      </c>
+      <c r="B105">
+        <v>1.85985824109061</v>
+      </c>
+      <c r="C105">
+        <v>-1.47180264072702</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>105</t>
+        </is>
+      </c>
+      <c r="B106">
+        <v>-0.8658304178485945</v>
+      </c>
+      <c r="C106">
+        <v>0.5309964935798783</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>106</t>
+        </is>
+      </c>
+      <c r="B107">
+        <v>0.7121776805886507</v>
+      </c>
+      <c r="C107">
+        <v>-1.050007089921323</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>107</t>
+        </is>
+      </c>
+      <c r="B108">
+        <v>1.171476617590892</v>
+      </c>
+      <c r="C108">
+        <v>0.04988444317013591</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>108</t>
+        </is>
+      </c>
+      <c r="B109">
+        <v>1.575382319091891</v>
+      </c>
+      <c r="C109">
+        <v>0.7770164326709772</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="B110">
+        <v>-1.371388674732815</v>
+      </c>
+      <c r="C110">
+        <v>1.237323155202209</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="B111">
+        <v>1.616407805955808</v>
+      </c>
+      <c r="C111">
+        <v>-1.306243666840956</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>111</t>
+        </is>
+      </c>
+      <c r="B112">
+        <v>0.9648762504177036</v>
+      </c>
+      <c r="C112">
+        <v>0.5795252374689903</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="B113">
+        <v>1.149375447046259</v>
+      </c>
+      <c r="C113">
+        <v>-1.2619694355578</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>113</t>
+        </is>
+      </c>
+      <c r="B114">
+        <v>-2.012321209532941</v>
+      </c>
+      <c r="C114">
+        <v>1.06692395354259</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>114</t>
+        </is>
+      </c>
+      <c r="B115">
+        <v>-2.091888823583476</v>
+      </c>
+      <c r="C115">
+        <v>0.06416299265880632</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>115</t>
+        </is>
+      </c>
+      <c r="B116">
+        <v>0.4720700433781844</v>
+      </c>
+      <c r="C116">
+        <v>-1.038603392626632</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="B117">
+        <v>-0.1994378764090537</v>
+      </c>
+      <c r="C117">
+        <v>1.242184079167526</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>117</t>
+        </is>
+      </c>
+      <c r="B118">
+        <v>0.0003821423152504257</v>
+      </c>
+      <c r="C118">
+        <v>0.1405478052100988</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>118</t>
+        </is>
+      </c>
+      <c r="B119">
+        <v>1.768385480726686</v>
+      </c>
+      <c r="C119">
+        <v>-1.63944349333016</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>119</t>
+        </is>
+      </c>
+      <c r="B120">
+        <v>-1.084721320496217</v>
+      </c>
+      <c r="C120">
+        <v>-0.5458203859274067</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="B121">
+        <v>0.6721737142947746</v>
+      </c>
+      <c r="C121">
+        <v>-0.8121951192275501</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>121</t>
+        </is>
+      </c>
+      <c r="B122">
+        <v>-0.127871745547547</v>
+      </c>
+      <c r="C122">
+        <v>0.06451078540254397</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>122</t>
+        </is>
+      </c>
+      <c r="B123">
+        <v>-0.2511053863787527</v>
+      </c>
+      <c r="C123">
+        <v>0.1158357349188124</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>123</t>
+        </is>
+      </c>
+      <c r="B124">
+        <v>-0.9673050309014387</v>
+      </c>
+      <c r="C124">
+        <v>0.1546663039769983</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>124</t>
+        </is>
+      </c>
+      <c r="B125">
+        <v>0.8328952704324502</v>
+      </c>
+      <c r="C125">
+        <v>0.05916501556033743</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>125</t>
+        </is>
+      </c>
+      <c r="B126">
+        <v>-0.9283834852625718</v>
+      </c>
+      <c r="C126">
+        <v>0.04353389077499514</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>126</t>
+        </is>
+      </c>
+      <c r="B127">
+        <v>-0.9702669243710588</v>
+      </c>
+      <c r="C127">
+        <v>2.112834151331475</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>127</t>
+        </is>
+      </c>
+      <c r="B128">
+        <v>-0.9399125452409688</v>
+      </c>
+      <c r="C128">
+        <v>0.3445796085049144</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>128</t>
+        </is>
+      </c>
+      <c r="B129">
+        <v>0.7062600905499384</v>
+      </c>
+      <c r="C129">
+        <v>-1.390670830673321</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>129</t>
+        </is>
+      </c>
+      <c r="B130">
+        <v>-0.09050687319174965</v>
+      </c>
+      <c r="C130">
+        <v>-0.2722260714593162</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="B131">
+        <v>0.666009702711528</v>
+      </c>
+      <c r="C131">
+        <v>1.007732943321444</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="B132">
+        <v>-0.668838707261342</v>
+      </c>
+      <c r="C132">
+        <v>-1.354826418251524</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>132</t>
+        </is>
+      </c>
+      <c r="B133">
+        <v>-0.06495593054992124</v>
+      </c>
+      <c r="C133">
+        <v>0.8790639069239242</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>133</t>
+        </is>
+      </c>
+      <c r="B134">
+        <v>0.4899429786910837</v>
+      </c>
+      <c r="C134">
+        <v>-0.6286519546451456</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>134</t>
+        </is>
+      </c>
+      <c r="B135">
+        <v>0.1489283292918571</v>
+      </c>
+      <c r="C135">
+        <v>-0.4024575264944148</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>135</t>
+        </is>
+      </c>
+      <c r="B136">
+        <v>1.391405281793978</v>
+      </c>
+      <c r="C136">
+        <v>-0.2072326088754578</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>136</t>
+        </is>
+      </c>
+      <c r="B137">
+        <v>1.873021177611241</v>
+      </c>
+      <c r="C137">
+        <v>-1.114852851393183</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>137</t>
+        </is>
+      </c>
+      <c r="B138">
+        <v>1.043545533664997</v>
+      </c>
+      <c r="C138">
+        <v>0.2940665599167389</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>138</t>
+        </is>
+      </c>
+      <c r="B139">
+        <v>0.002572395350437751</v>
+      </c>
+      <c r="C139">
+        <v>-0.7550828724094187</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>139</t>
+        </is>
+      </c>
+      <c r="B140">
+        <v>-0.603756421436642</v>
+      </c>
+      <c r="C140">
+        <v>0.6291613811505687</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>140</t>
+        </is>
+      </c>
+      <c r="B141">
+        <v>1.15882150246209</v>
+      </c>
+      <c r="C141">
+        <v>-0.1467662850070436</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>141</t>
+        </is>
+      </c>
+      <c r="B142">
+        <v>0.915429432065671</v>
+      </c>
+      <c r="C142">
+        <v>-1.11934313164708</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>142</t>
+        </is>
+      </c>
+      <c r="B143">
+        <v>-0.8822210254034217</v>
+      </c>
+      <c r="C143">
+        <v>0.2839029322586486</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>143</t>
+        </is>
+      </c>
+      <c r="B144">
+        <v>1.186946545843136</v>
+      </c>
+      <c r="C144">
+        <v>0.4155817890870029</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>144</t>
+        </is>
+      </c>
+      <c r="B145">
+        <v>1.456883030174842</v>
+      </c>
+      <c r="C145">
+        <v>0.8573532820435998</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>145</t>
+        </is>
+      </c>
+      <c r="B146">
+        <v>0.3933743733488482</v>
+      </c>
+      <c r="C146">
+        <v>-0.4619162368536891</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>146</t>
+        </is>
+      </c>
+      <c r="B147">
+        <v>-1.102108826590445</v>
+      </c>
+      <c r="C147">
+        <v>-0.14723743329488</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>147</t>
+        </is>
+      </c>
+      <c r="B148">
+        <v>-0.5766864511334294</v>
+      </c>
+      <c r="C148">
+        <v>-0.8115377721429869</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>148</t>
+        </is>
+      </c>
+      <c r="B149">
+        <v>0.9150408035460882</v>
+      </c>
+      <c r="C149">
+        <v>1.283367723822099</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>149</t>
+        </is>
+      </c>
+      <c r="B150">
+        <v>1.770339677340386</v>
+      </c>
+      <c r="C150">
+        <v>0.2085069947656067</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="B151">
+        <v>-0.7950449008189151</v>
+      </c>
+      <c r="C151">
+        <v>-1.186362604857838</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>151</t>
+        </is>
+      </c>
+      <c r="B152">
+        <v>0.04028003731830614</v>
+      </c>
+      <c r="C152">
+        <v>0.561159928364218</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>152</t>
+        </is>
+      </c>
+      <c r="B153">
+        <v>-2.004205494727128</v>
+      </c>
+      <c r="C153">
+        <v>0.4842386886137721</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>153</t>
+        </is>
+      </c>
+      <c r="B154">
+        <v>-1.761869766557767</v>
+      </c>
+      <c r="C154">
+        <v>1.145434476947805</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>154</t>
+        </is>
+      </c>
+      <c r="B155">
+        <v>1.478366254745693</v>
+      </c>
+      <c r="C155">
+        <v>-0.235417471945293</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>155</t>
+        </is>
+      </c>
+      <c r="B156">
+        <v>0.1995210162964135</v>
+      </c>
+      <c r="C156">
+        <v>2.244976175543245</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>156</t>
+        </is>
+      </c>
+      <c r="B157">
+        <v>-0.3543974081201182</v>
+      </c>
+      <c r="C157">
+        <v>-0.9812942080345536</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>157</t>
+        </is>
+      </c>
+      <c r="B158">
+        <v>-1.032228796307007</v>
+      </c>
+      <c r="C158">
+        <v>1.546866455781569</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>158</t>
+        </is>
+      </c>
+      <c r="B159">
+        <v>0.04054246547152173</v>
+      </c>
+      <c r="C159">
+        <v>-0.4957255122427365</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>159</t>
+        </is>
+      </c>
+      <c r="B160">
+        <v>-0.8295339878525188</v>
+      </c>
+      <c r="C160">
+        <v>0.2222629312271099</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="B161">
+        <v>0.4683535963753736</v>
+      </c>
+      <c r="C161">
+        <v>-2.019072841625681</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>161</t>
+        </is>
+      </c>
+      <c r="B162">
+        <v>-1.266848577895041</v>
+      </c>
+      <c r="C162">
+        <v>-0.1952018271584242</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>162</t>
+        </is>
+      </c>
+      <c r="B163">
+        <v>0.2511387153364374</v>
+      </c>
+      <c r="C163">
+        <v>-0.9433778649125222</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>163</t>
+        </is>
+      </c>
+      <c r="B164">
+        <v>1.14526341046566</v>
+      </c>
+      <c r="C164">
+        <v>-1.176483293514552</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>164</t>
+        </is>
+      </c>
+      <c r="B165">
+        <v>-0.2668461290189542</v>
+      </c>
+      <c r="C165">
+        <v>-0.0385477602929164</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>165</t>
+        </is>
+      </c>
+      <c r="B166">
+        <v>2.133107816088338</v>
+      </c>
+      <c r="C166">
+        <v>-0.1419812700958006</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>166</t>
+        </is>
+      </c>
+      <c r="B167">
+        <v>0.5244096278781939</v>
+      </c>
+      <c r="C167">
+        <v>-0.4787202536832643</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>167</t>
+        </is>
+      </c>
+      <c r="B168">
+        <v>1.422236209773296</v>
+      </c>
+      <c r="C168">
+        <v>-1.056196149136333</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>168</t>
+        </is>
+      </c>
+      <c r="B169">
+        <v>-1.061714497000799</v>
+      </c>
+      <c r="C169">
+        <v>0.1364146908057216</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>169</t>
+        </is>
+      </c>
+      <c r="B170">
+        <v>0.257168439643447</v>
+      </c>
+      <c r="C170">
+        <v>-0.1221272296303602</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>170</t>
+        </is>
+      </c>
+      <c r="B171">
+        <v>0.4841656743899818</v>
+      </c>
+      <c r="C171">
+        <v>0.9371459411609362</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>171</t>
+        </is>
+      </c>
+      <c r="B172">
+        <v>0.121019171408047</v>
+      </c>
+      <c r="C172">
+        <v>0.1391230409771289</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>172</t>
+        </is>
+      </c>
+      <c r="B173">
+        <v>-0.7896560450646204</v>
+      </c>
+      <c r="C173">
+        <v>-0.4388886423271707</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>173</t>
+        </is>
+      </c>
+      <c r="B174">
+        <v>0.1354076612089328</v>
+      </c>
+      <c r="C174">
+        <v>-0.7592649587221197</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>174</t>
+        </is>
+      </c>
+      <c r="B175">
+        <v>0.03483812077933029</v>
+      </c>
+      <c r="C175">
+        <v>1.360696795432827</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>175</t>
+        </is>
+      </c>
+      <c r="B176">
+        <v>0.6583549711535671</v>
+      </c>
+      <c r="C176">
+        <v>-1.24471053107406</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>176</t>
+        </is>
+      </c>
+      <c r="B177">
+        <v>-0.4203228107216632</v>
+      </c>
+      <c r="C177">
+        <v>0.9703952970292888</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>177</t>
+        </is>
+      </c>
+      <c r="B178">
+        <v>-1.972154094280545</v>
+      </c>
+      <c r="C178">
+        <v>1.682092794422509</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>178</t>
+        </is>
+      </c>
+      <c r="B179">
+        <v>0.355579401358196</v>
+      </c>
+      <c r="C179">
+        <v>0.6681885518446491</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>179</t>
+        </is>
+      </c>
+      <c r="B180">
+        <v>-0.7598852338636705</v>
+      </c>
+      <c r="C180">
+        <v>0.8792946070795347</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="B181">
+        <v>1.100091159452401</v>
+      </c>
+      <c r="C181">
+        <v>-1.498314603440034</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>181</t>
+        </is>
+      </c>
+      <c r="B182">
+        <v>-0.2138697062292028</v>
+      </c>
+      <c r="C182">
+        <v>0.5168666034302787</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>182</t>
+        </is>
+      </c>
+      <c r="B183">
+        <v>-2.330955155563722</v>
+      </c>
+      <c r="C183">
+        <v>1.677541240274872</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>183</t>
+        </is>
+      </c>
+      <c r="B184">
+        <v>0.01926819857856015</v>
+      </c>
+      <c r="C184">
+        <v>-0.7701388120577721</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>184</t>
+        </is>
+      </c>
+      <c r="B185">
+        <v>-1.116506903680313</v>
+      </c>
+      <c r="C185">
+        <v>-0.6581534946205816</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>185</t>
+        </is>
+      </c>
+      <c r="B186">
+        <v>1.856204420654538</v>
+      </c>
+      <c r="C186">
+        <v>-0.4616559805039586</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>186</t>
+        </is>
+      </c>
+      <c r="B187">
+        <v>-0.07709773658016965</v>
+      </c>
+      <c r="C187">
+        <v>-0.01513272664937684</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>187</t>
+        </is>
+      </c>
+      <c r="B188">
+        <v>-0.2851678073766373</v>
+      </c>
+      <c r="C188">
+        <v>1.404597243749096</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>188</t>
+        </is>
+      </c>
+      <c r="B189">
+        <v>-0.6348343916079562</v>
+      </c>
+      <c r="C189">
+        <v>0.02983020520175361</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>189</t>
+        </is>
+      </c>
+      <c r="B190">
+        <v>1.506919223723426</v>
+      </c>
+      <c r="C190">
+        <v>-0.5662150208830069</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>190</t>
+        </is>
+      </c>
+      <c r="B191">
+        <v>-0.004172005344299526</v>
+      </c>
+      <c r="C191">
+        <v>-0.8984358032799938</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>191</t>
+        </is>
+      </c>
+      <c r="B192">
+        <v>0.334105459926238</v>
+      </c>
+      <c r="C192">
+        <v>-0.8459701100386343</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>192</t>
+        </is>
+      </c>
+      <c r="B193">
+        <v>0.1969787459093685</v>
+      </c>
+      <c r="C193">
+        <v>-0.3135717200890786</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>193</t>
+        </is>
+      </c>
+      <c r="B194">
+        <v>-0.08547803518057911</v>
+      </c>
+      <c r="C194">
+        <v>0.4435610253629429</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>194</t>
+        </is>
+      </c>
+      <c r="B195">
+        <v>-0.2785619608954835</v>
+      </c>
+      <c r="C195">
+        <v>-1.099943925457673</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>195</t>
+        </is>
+      </c>
+      <c r="B196">
+        <v>1.406476636529742</v>
+      </c>
+      <c r="C196">
+        <v>0.8437037165748039</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>196</t>
+        </is>
+      </c>
+      <c r="B197">
+        <v>0.5650597672012543</v>
+      </c>
+      <c r="C197">
+        <v>-0.5561898052833929</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>197</t>
+        </is>
+      </c>
+      <c r="B198">
+        <v>0.9326237564936917</v>
+      </c>
+      <c r="C198">
+        <v>0.08630389792379722</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>198</t>
+        </is>
+      </c>
+      <c r="B199">
+        <v>-0.9878348634120343</v>
+      </c>
+      <c r="C199">
+        <v>0.3572756001056403</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>199</t>
+        </is>
+      </c>
+      <c r="B200">
+        <v>-0.9690063836581129</v>
+      </c>
+      <c r="C200">
+        <v>-0.396685090610352</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="B201">
+        <v>-1.224146426771822</v>
+      </c>
+      <c r="C201">
+        <v>0.3568390325384156</v>
       </c>
     </row>
   </sheetData>
